--- a/samples/output/sample_realistic_data_audit_findings.xlsx
+++ b/samples/output/sample_realistic_data_audit_findings.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Findings'!$A$1:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Findings'!$A$1:$K$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15 09:02:02</t>
+          <t>2026-07-27 16:58:36</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>Mixed phone formats: 3 values deviate from (XXX) XXX-XXXX</t>
+          <t>Mixed phone formats: 3 of 27 values deviate from (XXX) XXX-XXXX</t>
         </is>
       </c>
       <c r="G2" s="6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>Mixed date formats: 3 values deviate from YYYY-MM-DD</t>
+          <t>Mixed date formats: 3 of 28 values deviate from YYYY-MM-DD</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Mixed currency formats: 2 values deviate from $X,XXX.XX</t>
+          <t>Mixed currency formats: 2 of 28 values deviate from $X,XXX.XX</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>"$49.00" repeated 21 times</t>
+          <t>Suspicious repetition: "$49.00" appears 21 times (75.0%)</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>"$79.00" repeated 5 times</t>
+          <t>Suspicious repetition: "$79.00" appears 5 times (17.9%)</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Inconsistent casing in categorical values</t>
+          <t>Inconsistent casing in categorical values: e.g. "Active / active"</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>"Active" repeated 25 times</t>
+          <t>Suspicious repetition: "Active" appears 25 times (89.3%)</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>20 of 28 values missing (71.4%)</t>
+          <t>High missing rate: 20 of 28 values missing (71.4%)</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>Placeholder "TBD" found 1 times</t>
+          <t>Placeholder: "TBD" appears 1 times (12.5%)</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I12"/>
+  <autoFilter ref="A1:K12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/samples/output/sample_realistic_data_audit_findings.xlsx
+++ b/samples/output/sample_realistic_data_audit_findings.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27 16:58:36</t>
+          <t>2026-07-31 21:22:53</t>
         </is>
       </c>
     </row>

--- a/samples/output/sample_realistic_data_audit_findings.xlsx
+++ b/samples/output/sample_realistic_data_audit_findings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Findings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Findings'!$A$1:$K$12</definedName>
@@ -540,7 +540,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27 16:58:36</t>
+          <t>2026-08-05 20:45:09</t>
         </is>
       </c>
     </row>
